--- a/experiment_results/wu_calibration/rtt_bursts_rps5_att4_WU500000.xlsx
+++ b/experiment_results/wu_calibration/rtt_bursts_rps5_att4_WU500000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.7</t>
+          <t>00:010.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:018.1</t>
+          <t>00:018.9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>414.5</t>
+          <t>409.4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>577.7</t>
+          <t>541.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>98.66</t>
+          <t>104.23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>258190</t>
+          <t>275312</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:024.4</t>
+          <t>00:024.3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1107.8</t>
+          <t>922.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>484.7</t>
+          <t>492.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>568262</t>
+          <t>583782</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:036.1</t>
+          <t>00:035.9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1459.1</t>
+          <t>1298.7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>424.2</t>
+          <t>396.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>628393</t>
+          <t>624518</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:054.2</t>
+          <t>00:053.6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>870.2</t>
+          <t>1452.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>374.1</t>
+          <t>333.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>683174</t>
+          <t>692993</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:059.3</t>
+          <t>00:056.6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>746.9</t>
+          <t>1510.4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>347.6</t>
+          <t>308.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>752965</t>
+          <t>771683</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.9</t>
+          <t>01:010.6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>903.8</t>
+          <t>1421.7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>427.0</t>
+          <t>400.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>853751</t>
+          <t>819147</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:015.2</t>
+          <t>01:018.8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1143.9</t>
+          <t>1540.2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>439.8</t>
+          <t>326.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>941956</t>
+          <t>879728</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,22 +932,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:034.3</t>
+          <t>01:025.6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1085.6</t>
+          <t>1716.8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>511.8</t>
+          <t>240.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>991692</t>
+          <t>922005</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -981,462 +981,6 @@
         </is>
       </c>
       <c r="K10" t="inlineStr">
-        <is>
-          <t>DDoS Burst</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>01:039.3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1234.2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>485.1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1080996</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>DDoS Burst</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>01:049.0</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1632.9</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>297.0</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1182143</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>DDoS Burst</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>02:000.8</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1126.5</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>573.4</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1268971</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>DDoS Burst</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>02:010.8</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>803.9</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>418.7</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1355160</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>DDoS Burst</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>02:020.7</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>789.5</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>436.7</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1447375</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>DDoS Burst</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>02:031.9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>647.8</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.64</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1546019</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>DDoS Burst</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>02:035.8</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>622.7</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>257.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1611504</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>DDoS Burst</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>02:040.5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>904.4</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>234.3</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1620273</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
         <is>
           <t>DDoS Burst</t>
         </is>
